--- a/Relatorio_Faturamento.xlsx
+++ b/Relatorio_Faturamento.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -498,33 +498,31 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4579.57</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>6048.5</v>
+        <v>3500.5</v>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="H2" t="n">
         <v>2026</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46055</v>
+        <v>46083</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -536,33 +534,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2688.76</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2024.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G3" t="n">
-        <v>43.07</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2026</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -574,33 +564,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2784.41</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2597.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>54</v>
-      </c>
-      <c r="G4" t="n">
-        <v>48.1</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2026</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46057</v>
+        <v>46085</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -612,33 +594,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2935.91</v>
-      </c>
-      <c r="F5" t="n">
-        <v>58</v>
-      </c>
-      <c r="G5" t="n">
-        <v>50.62</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2026</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,33 +624,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3353.45</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3079.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>73</v>
-      </c>
-      <c r="G6" t="n">
-        <v>42.18</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2026</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46059</v>
+        <v>46087</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -688,33 +654,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>3092.86</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2657.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G7" t="n">
-        <v>40.88</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2026</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46060</v>
+        <v>46088</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -726,33 +684,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>4778.57</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5130</v>
-      </c>
-      <c r="F8" t="n">
-        <v>115</v>
-      </c>
-      <c r="G8" t="n">
-        <v>44.61</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2026</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46061</v>
+        <v>46089</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -764,33 +714,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>4579.57</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7023.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>139</v>
-      </c>
-      <c r="G9" t="n">
-        <v>50.53</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2026</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46062</v>
+        <v>46090</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -802,33 +744,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2688.76</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3674</v>
-      </c>
-      <c r="F10" t="n">
-        <v>71</v>
-      </c>
-      <c r="G10" t="n">
-        <v>51.75</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2026</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46063</v>
+        <v>46091</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -840,33 +774,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2784.41</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3054.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>65</v>
-      </c>
-      <c r="G11" t="n">
-        <v>46.99</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2026</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46064</v>
+        <v>46092</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -878,33 +804,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4457</v>
-      </c>
-      <c r="F12" t="n">
-        <v>77</v>
-      </c>
-      <c r="G12" t="n">
-        <v>57.88</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2026</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46065</v>
+        <v>46093</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -916,33 +834,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3353.45</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1257</v>
-      </c>
-      <c r="F13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G13" t="n">
-        <v>34.92</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2026</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -954,33 +864,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>3092.86</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1471.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>37</v>
-      </c>
-      <c r="G14" t="n">
-        <v>39.77</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2026</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46067</v>
+        <v>46095</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -992,33 +894,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>4778.57</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3689.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>61</v>
-      </c>
-      <c r="G15" t="n">
-        <v>60.48</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2026</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46068</v>
+        <v>46096</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1030,33 +924,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>4579.57</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2867.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>53</v>
-      </c>
-      <c r="G16" t="n">
-        <v>54.1</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2026</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1068,33 +954,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>2688.76</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2008.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>42</v>
-      </c>
-      <c r="G17" t="n">
-        <v>47.82</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2026</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46070</v>
+        <v>46098</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1106,33 +984,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>2784.41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2237</v>
-      </c>
-      <c r="F18" t="n">
-        <v>54</v>
-      </c>
-      <c r="G18" t="n">
-        <v>41.43</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2026</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46071</v>
+        <v>46099</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1144,33 +1014,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1707.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>49</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.85</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2026</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46072</v>
+        <v>46100</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1182,47 +1044,37 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>3353.45</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1749.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>45</v>
-      </c>
-      <c r="G20" t="n">
-        <v>38.88</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2026</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46074</v>
+        <v>46101</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>sexta-feira</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4778.57</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1230,31 +1082,29 @@
         <v>2026</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46075</v>
+        <v>46102</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>domingo</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4579.57</v>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1262,31 +1112,29 @@
         <v>2026</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46076</v>
+        <v>46103</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>segunda-feira</t>
+          <t>domingo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2688.76</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1294,31 +1142,29 @@
         <v>2026</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46077</v>
+        <v>46104</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>terça-feira</t>
+          <t>segunda-feira</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2784.41</v>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1326,31 +1172,29 @@
         <v>2026</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46078</v>
+        <v>46105</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>quarta-feira</t>
+          <t>terça-feira</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3123.95</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1358,31 +1202,29 @@
         <v>2026</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46079</v>
+        <v>46106</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>quinta-feira</t>
+          <t>quarta-feira</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>3353.45</v>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1390,31 +1232,29 @@
         <v>2026</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46080</v>
+        <v>46107</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sexta-feira</t>
+          <t>quinta-feira</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3092.86</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1422,31 +1262,29 @@
         <v>2026</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46081</v>
+        <v>46108</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>sexta-feira</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4778.57</v>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1454,21 +1292,21 @@
         <v>2026</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46073</v>
+        <v>46109</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sexta-feira</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1476,27 +1314,109 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>3092.86</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2585.4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" t="n">
-        <v>49.72</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2026</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Março</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>segunda-feira</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>terça-feira</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Março</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Faturamento.xlsx
+++ b/Relatorio_Faturamento.xlsx
@@ -535,9 +535,15 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>1674.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41.86</v>
+      </c>
       <c r="H3" t="n">
         <v>2026</v>
       </c>
@@ -565,9 +571,15 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>3251</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45.15</v>
+      </c>
       <c r="H4" t="n">
         <v>2026</v>
       </c>

--- a/Relatorio_Faturamento.xlsx
+++ b/Relatorio_Faturamento.xlsx
@@ -607,9 +607,15 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2356</v>
+      </c>
+      <c r="F5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51.22</v>
+      </c>
       <c r="H5" t="n">
         <v>2026</v>
       </c>
@@ -637,9 +643,15 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1897.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.37</v>
+      </c>
       <c r="H6" t="n">
         <v>2026</v>
       </c>

--- a/Relatorio_Faturamento.xlsx
+++ b/Relatorio_Faturamento.xlsx
@@ -498,7 +498,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>4694.98</v>
+      </c>
       <c r="E2" t="n">
         <v>3500.5</v>
       </c>
@@ -534,7 +536,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2600.96</v>
+      </c>
       <c r="E3" t="n">
         <v>1674.5</v>
       </c>
@@ -570,7 +574,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2691.1</v>
+      </c>
       <c r="E4" t="n">
         <v>3251</v>
       </c>
@@ -606,7 +612,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>3000.22</v>
+      </c>
       <c r="E5" t="n">
         <v>2356</v>
       </c>
@@ -642,7 +650,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>3049.44</v>
+      </c>
       <c r="E6" t="n">
         <v>1897.5</v>
       </c>
@@ -678,10 +688,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>3011.87</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>49.55</v>
+      </c>
       <c r="H7" t="n">
         <v>2026</v>
       </c>
@@ -708,10 +726,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>4793.87</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3803.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" t="n">
+        <v>47.54</v>
+      </c>
       <c r="H8" t="n">
         <v>2026</v>
       </c>
@@ -738,10 +764,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>4694.98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3740.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>47.35</v>
+      </c>
       <c r="H9" t="n">
         <v>2026</v>
       </c>
@@ -768,10 +802,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2600.96</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2013.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>47.94</v>
+      </c>
       <c r="H10" t="n">
         <v>2026</v>
       </c>
@@ -798,10 +840,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>2691.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2396</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>46.08</v>
+      </c>
       <c r="H11" t="n">
         <v>2026</v>
       </c>
@@ -828,10 +878,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>3000.22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5202</v>
+      </c>
+      <c r="F12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G12" t="n">
+        <v>76.5</v>
+      </c>
       <c r="H12" t="n">
         <v>2026</v>
       </c>
@@ -858,10 +916,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>3049.44</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2442.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>51.97</v>
+      </c>
       <c r="H13" t="n">
         <v>2026</v>
       </c>
@@ -888,10 +954,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>3011.87</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="n">
+        <v>41.58</v>
+      </c>
       <c r="H14" t="n">
         <v>2026</v>
       </c>
@@ -918,10 +992,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>4793.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2945.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>59</v>
+      </c>
+      <c r="G15" t="n">
+        <v>49.92</v>
+      </c>
       <c r="H15" t="n">
         <v>2026</v>
       </c>
@@ -948,10 +1030,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>4694.98</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2583</v>
+      </c>
+      <c r="F16" t="n">
+        <v>51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50.65</v>
+      </c>
       <c r="H16" t="n">
         <v>2026</v>
       </c>
@@ -978,10 +1068,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2600.96</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1635.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40.89</v>
+      </c>
       <c r="H17" t="n">
         <v>2026</v>
       </c>
@@ -1008,10 +1106,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>2691.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2055.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>41.95</v>
+      </c>
       <c r="H18" t="n">
         <v>2026</v>
       </c>
@@ -1038,10 +1144,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>3000.22</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42.2</v>
+      </c>
       <c r="H19" t="n">
         <v>2026</v>
       </c>
@@ -1068,10 +1182,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>3049.44</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2001.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>49</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40.85</v>
+      </c>
       <c r="H20" t="n">
         <v>2026</v>
       </c>
@@ -1098,10 +1220,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>3011.87</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2674</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43</v>
+      </c>
+      <c r="G21" t="n">
+        <v>62.19</v>
+      </c>
       <c r="H21" t="n">
         <v>2026</v>
       </c>
@@ -1128,10 +1258,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>4793.87</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3262.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>72</v>
+      </c>
+      <c r="G22" t="n">
+        <v>45.31</v>
+      </c>
       <c r="H22" t="n">
         <v>2026</v>
       </c>
@@ -1158,10 +1296,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>4694.98</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3460</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G23" t="n">
+        <v>49.43</v>
+      </c>
       <c r="H23" t="n">
         <v>2026</v>
       </c>
@@ -1188,10 +1334,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>2600.96</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22</v>
+      </c>
+      <c r="G24" t="n">
+        <v>49.09</v>
+      </c>
       <c r="H24" t="n">
         <v>2026</v>
       </c>
@@ -1218,10 +1372,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>2691.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2301</v>
+      </c>
+      <c r="F25" t="n">
+        <v>48</v>
+      </c>
+      <c r="G25" t="n">
+        <v>47.94</v>
+      </c>
       <c r="H25" t="n">
         <v>2026</v>
       </c>
@@ -1248,10 +1410,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>3000.22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2330.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>44</v>
+      </c>
+      <c r="G26" t="n">
+        <v>52.97</v>
+      </c>
       <c r="H26" t="n">
         <v>2026</v>
       </c>
@@ -1278,7 +1448,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>3049.44</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1308,7 +1480,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>3011.87</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1338,7 +1512,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>4793.87</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1368,7 +1544,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>4694.98</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1398,7 +1576,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>2600.96</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1428,7 +1608,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>2691.1</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
